--- a/amitdusane-site-complete/static/templates/adobe-analytics-validation-report-template.xlsx
+++ b/amitdusane-site-complete/static/templates/adobe-analytics-validation-report-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ed449a1af7f163/Documents/Claude Code/Adobe Analytics/amitdusane-site-complete/static/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FA1384B-B1F5-4FA4-BAAF-D2AC4238BF1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A413A7E5-04E4-4372-9464-CA38E43D2A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{80C362DC-CC94-4120-BB52-872EF7F09495}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{52B0F649-6D67-49BE-A935-437FBE81D9E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{BD5A811C-7D44-4440-9FE8-2248D2D4F524}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{9AA4C8C5-0BA4-4F2D-BCEB-BE853CB89B4B}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{9936EBEF-2543-451C-B0B8-3517BD845B9B}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{67569A2D-A43C-4103-A458-847241387864}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{5AC67581-8EC6-4DA4-A305-9698739E2B9B}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{3E2A9B3A-DACA-4CDA-83BB-9CD86B588F9B}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{EFA56844-0C36-4A9E-A3BA-742B4161E343}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{EF6F3FB2-FC38-4F83-A56E-A5958BF986DA}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{423DE6BF-F533-45EC-BEC0-DFB1FADF990A}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{D25D1DEA-712B-47E3-99F3-2369DE096238}">
       <text>
         <r>
           <rPr>
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{4EBA9A19-A13B-4070-AF69-A8FA91F6812A}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{2B571EF6-231C-48A8-A7E2-E360ACD02B6E}">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{8EEA1F60-C83F-49CD-9909-C416659D6B10}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{F1E43C66-1866-4F94-A023-9A4FDB9114F2}">
       <text>
         <r>
           <rPr>
@@ -141,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{C3A102DB-90D5-428A-85F3-6E74367A306C}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{CC1C6CEC-0014-4A5E-8B94-E8284EEB7A2A}">
       <text>
         <r>
           <rPr>
@@ -151,7 +151,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Filled in by Kestrel and Co., not by us.</t>
+          <t>Filled in by the Kestrel business team, not by the analytics team.</t>
         </r>
       </text>
     </comment>
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="123">
   <si>
     <t>Validation Report - Kestrel and Co. Website - Phase 1 - Staging</t>
   </si>
@@ -219,10 +219,7 @@
     <t>Named Day view deferred to the Phase 1 patch release, agreed 04 Jun.</t>
   </si>
   <si>
-    <t>Kestrel</t>
-  </si>
-  <si>
-    <t>12 Jun</t>
+    <t>Kestrel web dev</t>
   </si>
   <si>
     <t>KES-S003</t>
@@ -327,9 +324,6 @@
     <t>Numeric timeout codes accepted for launch and classified in reporting instead, agreed 04 Jun.</t>
   </si>
   <si>
-    <t>26 Jun</t>
-  </si>
-  <si>
     <t>KES-S014</t>
   </si>
   <si>
@@ -387,9 +381,6 @@
     <t>22 May: No call. 29 May: No call. 04 Jun: Still no call. The session is cleared and the page reloads before the tag manager can see anything.</t>
   </si>
   <si>
-    <t>19 Jun</t>
-  </si>
-  <si>
     <t>KES-S020</t>
   </si>
   <si>
@@ -462,6 +453,9 @@
     <t>04 Jun: Uploaded and applied. Twelve campaign codes classified, four with no name yet.</t>
   </si>
   <si>
+    <t>Kestrel marketing</t>
+  </si>
+  <si>
     <t>pre launch</t>
   </si>
   <si>
@@ -492,21 +486,12 @@
     <t>What it means here</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>Behaves as the SDR says, across three cycles, with evidence captured.</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>Works for the main case. A named part does not, and the part is written down with an owner and a date.</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Does not work. KES-S019 sign out. Still open with Kestrel and Co.</t>
   </si>
   <si>
@@ -516,34 +501,22 @@
     <t>Total solutions tested</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>Twenty four rules and four configuration items.</t>
   </si>
   <si>
     <t>Cycles run</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>22 May, 29 May, 04 June. All on staging.</t>
   </si>
   <si>
     <t>Faults found in cycle 1</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
     <t>Of twenty eight solutions tested, two were correct first time.</t>
   </si>
   <si>
     <t>Faults still open</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>Two exceptions accepted, one failure, one solution dropped.</t>
@@ -635,14 +608,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -958,7 +934,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2F8480-AA9F-4247-A600-9514272393B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E359A772-FA87-4442-9E69-17CD565F491B}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
@@ -1046,23 +1022,23 @@
       <c r="F5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>20</v>
+      <c r="G5" s="5">
+        <v>46185</v>
       </c>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
@@ -1073,16 +1049,16 @@
     </row>
     <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -1093,16 +1069,16 @@
     </row>
     <row r="8" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
@@ -1113,16 +1089,16 @@
     </row>
     <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -1133,16 +1109,16 @@
     </row>
     <row r="10" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
@@ -1153,16 +1129,16 @@
     </row>
     <row r="11" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1173,16 +1149,16 @@
     </row>
     <row r="12" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
@@ -1193,16 +1169,16 @@
     </row>
     <row r="13" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
@@ -1213,16 +1189,16 @@
     </row>
     <row r="14" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -1233,16 +1209,16 @@
     </row>
     <row r="15" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -1253,25 +1229,25 @@
     </row>
     <row r="16" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>55</v>
+      <c r="G16" s="5">
+        <v>46199</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>13</v>
@@ -1279,16 +1255,16 @@
     </row>
     <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -1299,16 +1275,16 @@
     </row>
     <row r="18" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
@@ -1319,16 +1295,16 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
@@ -1339,16 +1315,16 @@
     </row>
     <row r="20" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
@@ -1359,16 +1335,16 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
@@ -1379,38 +1355,38 @@
     </row>
     <row r="22" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>75</v>
+      <c r="G22" s="5">
+        <v>46192</v>
       </c>
       <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
@@ -1421,16 +1397,16 @@
     </row>
     <row r="24" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -1441,16 +1417,16 @@
     </row>
     <row r="25" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
@@ -1461,40 +1437,40 @@
     </row>
     <row r="26" spans="1:8" ht="57" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -1505,16 +1481,16 @@
     </row>
     <row r="28" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
@@ -1523,25 +1499,25 @@
       </c>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>13</v>
@@ -1549,16 +1525,16 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>103</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -1569,16 +1545,16 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -1588,14 +1564,14 @@
       <c r="H31" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H31" xr:uid="{1B2F8480-AA9F-4247-A600-9514272393B5}"/>
+  <autoFilter ref="A3:H31" xr:uid="{E359A772-FA87-4442-9E69-17CD565F491B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940C78D3-2E28-4963-97C4-68D556EFFBC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD4A6A3-F12B-46FD-A354-D6833EAD98C1}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
@@ -1610,7 +1586,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -1618,54 +1594,54 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>110</v>
+      <c r="B4" s="4">
+        <v>24</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>112</v>
+      <c r="B5" s="4">
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>114</v>
+        <v>71</v>
+      </c>
+      <c r="B6" s="4">
+        <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>114</v>
+        <v>84</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -1675,46 +1651,46 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>118</v>
+        <v>112</v>
+      </c>
+      <c r="B9" s="4">
+        <v>28</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>121</v>
+        <v>114</v>
+      </c>
+      <c r="B10" s="4">
+        <v>3</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>124</v>
+        <v>116</v>
+      </c>
+      <c r="B11" s="4">
+        <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>127</v>
+        <v>118</v>
+      </c>
+      <c r="B12" s="4">
+        <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -1724,13 +1700,13 @@
     </row>
     <row r="14" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/amitdusane-site-complete/static/templates/adobe-analytics-validation-report-template.xlsx
+++ b/amitdusane-site-complete/static/templates/adobe-analytics-validation-report-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25ed449a1af7f163/Documents/Claude Code/Adobe Analytics/amitdusane-site-complete/static/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A413A7E5-04E4-4372-9464-CA38E43D2A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8988C7FF-E906-496C-B04B-7770310DA0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{52B0F649-6D67-49BE-A935-437FBE81D9E7}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{725CA36A-344F-44FE-8379-EF7F3D420C30}"/>
   </bookViews>
   <sheets>
     <sheet name="Tracker" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <author>Amit Dusane</author>
   </authors>
   <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{9AA4C8C5-0BA4-4F2D-BCEB-BE853CB89B4B}">
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{C92674DD-DA51-444C-A49F-27AD6646B9B2}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{67569A2D-A43C-4103-A458-847241387864}">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{3165026B-6857-4113-B212-0E294D6591EC}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{3E2A9B3A-DACA-4CDA-83BB-9CD86B588F9B}">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{91650032-30C2-4FF6-8F3A-3B6B9D5FDEA4}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{EF6F3FB2-FC38-4F83-A56E-A5958BF986DA}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{DA9869CC-471B-473E-8FBD-3BA1954A12AD}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{D25D1DEA-712B-47E3-99F3-2369DE096238}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{7D70EB42-AFC2-40A8-ACD2-AEC1C6A22EFD}">
       <text>
         <r>
           <rPr>
@@ -113,7 +113,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{2B571EF6-231C-48A8-A7E2-E360ACD02B6E}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{BEE6D1B8-A224-4D4D-BF99-548FFE111CA4}">
       <text>
         <r>
           <rPr>
@@ -127,7 +127,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{F1E43C66-1866-4F94-A023-9A4FDB9114F2}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{8FD8B24C-AF8F-4415-97EB-F9EC1B0918FB}">
       <text>
         <r>
           <rPr>
@@ -141,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{CC1C6CEC-0014-4A5E-8B94-E8284EEB7A2A}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{2CCB5391-CCAE-45BA-B5B2-D3DC3769DD2E}">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="124">
   <si>
     <t>Validation Report - Kestrel and Co. Website - Phase 1 - Staging</t>
   </si>
@@ -475,6 +475,9 @@
   </si>
   <si>
     <t>29 May: Two rules fire before consent is answered. 04 Jun: All rules gated. No hit before an answer.</t>
+  </si>
+  <si>
+    <t>Template from amitdusane.com  |  Amit G Dusane</t>
   </si>
   <si>
     <t>Summary - Phase 1 as at 04 June 2026</t>
@@ -535,7 +538,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -565,6 +568,14 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -608,7 +619,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -621,6 +632,7 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,11 +946,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E359A772-FA87-4442-9E69-17CD565F491B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB4296FE-DADA-48BD-9ED9-3B5845BB5580}">
   <sheetPr>
     <tabColor rgb="FF0070C0"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14.59765625" style="2" customWidth="1"/>
@@ -1563,19 +1575,27 @@
       </c>
       <c r="H31" s="4"/>
     </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:H31" xr:uid="{E359A772-FA87-4442-9E69-17CD565F491B}"/>
+  <autoFilter ref="A3:H31" xr:uid="{AB4296FE-DADA-48BD-9ED9-3B5845BB5580}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BD4A6A3-F12B-46FD-A354-D6833EAD98C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D855704F-CF76-427C-9F95-8B5CC2ABF0C4}">
   <sheetPr>
     <tabColor rgb="FFA6A6A6"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="26.59765625" style="2" customWidth="1"/>
@@ -1586,7 +1606,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -1594,10 +1614,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -1608,7 +1628,7 @@
         <v>24</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
@@ -1619,7 +1639,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -1630,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
@@ -1641,7 +1661,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -1651,46 +1671,46 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" s="4">
         <v>28</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" s="4">
         <v>3</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="4">
         <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B12" s="4">
         <v>4</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -1700,16 +1720,24 @@
     </row>
     <row r="14" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A14" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;"Calibri"&amp;8&amp;K808080Template from amitdusane.com   |   Amit G Dusane&amp;R&amp;"Calibri"&amp;8&amp;K808080Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>